--- a/controle_faltas.xlsx
+++ b/controle_faltas.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
